--- a/TDXapp/tdxAppData/csIndex.xlsx
+++ b/TDXapp/tdxAppData/csIndex.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20745" windowHeight="9675"/>
+    <workbookView windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="指数列表" sheetId="1" r:id="rId1"/>
@@ -11725,12 +11725,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -12051,7 +12057,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -12075,16 +12081,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -12093,93 +12099,96 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12730,22 +12739,22 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="14.25" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -19238,26 +19247,26 @@
         <v>13</v>
       </c>
     </row>
-    <row r="284" spans="1:7">
-      <c r="A284" t="s">
+    <row r="284" s="2" customFormat="1" spans="1:7">
+      <c r="A284" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="B284" t="s">
+      <c r="B284" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="C284" t="s">
-        <v>384</v>
-      </c>
-      <c r="D284" t="s">
+      <c r="C284" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D284" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E284" t="s">
-        <v>62</v>
-      </c>
-      <c r="F284" t="s">
+      <c r="E284" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F284" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="G284" t="s">
+      <c r="G284" s="2" t="s">
         <v>13</v>
       </c>
     </row>
